--- a/research/traditional_assets/database/data/south_africa/south_africa_insurance_life.xlsx
+++ b/research/traditional_assets/database/data/south_africa/south_africa_insurance_life.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AQ9"/>
+  <dimension ref="A1:AQ8"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -579,7 +579,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -588,124 +588,124 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.07240000000000001</v>
+        <v>0.08135000000000001</v>
       </c>
       <c r="E2">
-        <v>-0.029</v>
+        <v>0.04485</v>
       </c>
       <c r="F2">
-        <v>0.551</v>
+        <v>0.158</v>
       </c>
       <c r="G2">
-        <v>0.038273672891205</v>
+        <v>0.1639437898360222</v>
       </c>
       <c r="H2">
-        <v>0.038273672891205</v>
+        <v>0.1639437898360222</v>
       </c>
       <c r="I2">
-        <v>0.06930755971789203</v>
+        <v>0.1294689782665797</v>
       </c>
       <c r="J2">
-        <v>0.04317414133612289</v>
+        <v>0.09071045940765238</v>
       </c>
       <c r="K2">
-        <v>1511.3</v>
+        <v>3197</v>
       </c>
       <c r="L2">
-        <v>0.03125297268234175</v>
+        <v>0.1209312881811132</v>
       </c>
       <c r="M2">
-        <v>927.1</v>
+        <v>956.4999999999999</v>
       </c>
       <c r="N2">
-        <v>0.03668167538438408</v>
+        <v>0.05265968574857684</v>
       </c>
       <c r="O2">
-        <v>0.6134453781512605</v>
+        <v>0.2991867375664685</v>
       </c>
       <c r="P2">
-        <v>807.2</v>
+        <v>843.9</v>
       </c>
       <c r="Q2">
-        <v>0.03193770722713281</v>
+        <v>0.04646054239751594</v>
       </c>
       <c r="R2">
-        <v>0.534109706874876</v>
+        <v>0.2639662183296841</v>
       </c>
       <c r="S2">
-        <v>119.8999999999999</v>
+        <v>112.5999999999999</v>
       </c>
       <c r="T2">
-        <v>0.1293280120806816</v>
+        <v>0.1177208572922111</v>
       </c>
       <c r="U2">
-        <v>11659.9</v>
+        <v>8567.4</v>
       </c>
       <c r="V2">
-        <v>0.461336066027807</v>
+        <v>0.4716744293594953</v>
       </c>
       <c r="W2">
-        <v>0.08942090451464584</v>
+        <v>0.1611984950712607</v>
       </c>
       <c r="X2">
-        <v>0.09647668082485035</v>
+        <v>0.1419195984728924</v>
       </c>
       <c r="Y2">
-        <v>-0.007055776310204515</v>
+        <v>0.01927889659836823</v>
       </c>
       <c r="Z2">
-        <v>5.981233884358125</v>
+        <v>2.818802860946861</v>
       </c>
       <c r="AA2">
-        <v>0.1255371754871372</v>
+        <v>0.4089928875661729</v>
       </c>
       <c r="AB2">
-        <v>0.0848193385401039</v>
+        <v>0.1276895126679738</v>
       </c>
       <c r="AC2">
-        <v>0.03914745117111</v>
+        <v>0.2812192716671988</v>
       </c>
       <c r="AD2">
-        <v>6568.01</v>
+        <v>4148.52</v>
       </c>
       <c r="AE2">
-        <v>0.00667360947507816</v>
+        <v>9.616780277833241</v>
       </c>
       <c r="AF2">
-        <v>6568.016673609475</v>
+        <v>4158.136780277833</v>
       </c>
       <c r="AG2">
-        <v>-5091.883326390524</v>
+        <v>-4409.263219722166</v>
       </c>
       <c r="AH2">
-        <v>0.2062675705317018</v>
+        <v>0.1862802865722514</v>
       </c>
       <c r="AI2">
-        <v>0.2574953985812594</v>
+        <v>0.2238646165117954</v>
       </c>
       <c r="AJ2">
-        <v>-0.2522942935014345</v>
+        <v>-0.3205679180737268</v>
       </c>
       <c r="AK2">
-        <v>-0.3677135921023219</v>
+        <v>-0.4406206730927052</v>
       </c>
       <c r="AL2">
-        <v>371.02</v>
+        <v>398.79</v>
       </c>
       <c r="AM2">
-        <v>371.02</v>
+        <v>398.79</v>
       </c>
       <c r="AN2">
-        <v>1.841838784949104</v>
+        <v>1.145452587575551</v>
       </c>
       <c r="AO2">
-        <v>9.033205757102044</v>
+        <v>8.582712705935453</v>
       </c>
       <c r="AP2">
-        <v>-1.427894933013458</v>
+        <v>-1.217446695287105</v>
       </c>
       <c r="AQ2">
-        <v>9.033205757102044</v>
+        <v>8.582712705935453</v>
       </c>
     </row>
     <row r="3">
@@ -725,121 +725,112 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.104</v>
+        <v>0.05230000000000001</v>
       </c>
       <c r="E3">
-        <v>-0.268</v>
+        <v>0.193</v>
       </c>
       <c r="G3">
-        <v>0.04741969352630809</v>
+        <v>0.1607674418604651</v>
       </c>
       <c r="H3">
-        <v>0.04741969352630809</v>
+        <v>0.1607674418604651</v>
       </c>
       <c r="I3">
-        <v>0.04220990656938187</v>
+        <v>0.1537209302325581</v>
       </c>
       <c r="J3">
-        <v>0.02110495328469094</v>
+        <v>0.07786473948626529</v>
       </c>
       <c r="K3">
-        <v>31.6</v>
+        <v>226.7</v>
       </c>
       <c r="L3">
-        <v>0.004199726220379304</v>
+        <v>0.05272093023255814</v>
       </c>
       <c r="M3">
-        <v>69</v>
+        <v>44.9</v>
       </c>
       <c r="N3">
-        <v>0.04085499437503701</v>
+        <v>0.03216793236853417</v>
       </c>
       <c r="O3">
-        <v>2.183544303797468</v>
+        <v>0.1980591089545655</v>
       </c>
       <c r="P3">
-        <v>25.6</v>
+        <v>44.9</v>
       </c>
       <c r="Q3">
-        <v>0.01515779501450648</v>
+        <v>0.03216793236853417</v>
       </c>
       <c r="R3">
-        <v>0.810126582278481</v>
+        <v>0.1980591089545655</v>
       </c>
       <c r="S3">
-        <v>43.4</v>
+        <v>0</v>
       </c>
       <c r="T3">
-        <v>0.6289855072463768</v>
+        <v>0</v>
       </c>
       <c r="U3">
-        <v>2670.9</v>
+        <v>1754.4</v>
       </c>
       <c r="V3">
-        <v>1.581443543134585</v>
+        <v>1.256913597936667</v>
       </c>
       <c r="W3">
-        <v>0.02531848409582566</v>
+        <v>0.1567990040116199</v>
       </c>
       <c r="X3">
-        <v>0.1081081452970267</v>
+        <v>0.164947168837823</v>
       </c>
       <c r="Y3">
-        <v>-0.08278966120120106</v>
-      </c>
-      <c r="Z3">
-        <v>245.0912052117272</v>
-      </c>
-      <c r="AA3">
-        <v>5.172638436482101</v>
+        <v>-0.008148164826203175</v>
       </c>
       <c r="AB3">
-        <v>0.0848193385401039</v>
-      </c>
-      <c r="AC3">
-        <v>5.087819097941997</v>
+        <v>0.1274153863894588</v>
       </c>
       <c r="AD3">
-        <v>792.9</v>
+        <v>793.6</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>792.9</v>
+        <v>793.6</v>
       </c>
       <c r="AG3">
-        <v>-1878</v>
+        <v>-960.8000000000001</v>
       </c>
       <c r="AH3">
-        <v>0.3194858570392457</v>
+        <v>0.3624737370969215</v>
       </c>
       <c r="AI3">
-        <v>0.3404611619219374</v>
+        <v>0.3420837105047631</v>
       </c>
       <c r="AJ3">
-        <v>9.931253305129566</v>
+        <v>-2.208735632183909</v>
       </c>
       <c r="AK3">
-        <v>5.491228070175438</v>
+        <v>-1.699027409372238</v>
       </c>
       <c r="AL3">
-        <v>63.7</v>
+        <v>142.1</v>
       </c>
       <c r="AM3">
-        <v>63.7</v>
+        <v>142.1</v>
       </c>
       <c r="AN3">
-        <v>2.222253363228699</v>
+        <v>1.147982062780269</v>
       </c>
       <c r="AO3">
-        <v>4.985871271585557</v>
+        <v>4.651653764954258</v>
       </c>
       <c r="AP3">
-        <v>-5.263452914798206</v>
+        <v>-1.389845219152322</v>
       </c>
       <c r="AQ3">
-        <v>4.985871271585557</v>
+        <v>4.651653764954258</v>
       </c>
     </row>
     <row r="4">
@@ -850,7 +841,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Clientèle Limited (JSE:CLI)</t>
+          <t>Sanlam Limited (JSE:SLM)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -859,121 +850,121 @@
         </is>
       </c>
       <c r="D4">
-        <v>0.07240000000000001</v>
+        <v>0.09210000000000002</v>
       </c>
       <c r="E4">
-        <v>-0.009050000000000001</v>
+        <v>0.0493</v>
       </c>
       <c r="G4">
-        <v>0.3215530114484818</v>
+        <v>0.2509785030408864</v>
       </c>
       <c r="H4">
-        <v>0.3215530114484818</v>
+        <v>0.2509785030408864</v>
       </c>
       <c r="I4">
-        <v>0.3140866102538576</v>
+        <v>0.1703518749785253</v>
       </c>
       <c r="J4">
-        <v>0.2132686859748416</v>
+        <v>0.1322894687845975</v>
       </c>
       <c r="K4">
-        <v>27.5</v>
+        <v>697.3</v>
       </c>
       <c r="L4">
-        <v>0.1368840219014435</v>
+        <v>0.08397663635816222</v>
       </c>
       <c r="M4">
-        <v>22.3</v>
+        <v>553.6999999999999</v>
       </c>
       <c r="N4">
-        <v>0.1044007490636704</v>
+        <v>0.09427569297827419</v>
       </c>
       <c r="O4">
-        <v>0.8109090909090909</v>
+        <v>0.7940628137100243</v>
       </c>
       <c r="P4">
-        <v>22.3</v>
+        <v>512.9</v>
       </c>
       <c r="Q4">
-        <v>0.1044007490636704</v>
+        <v>0.08732888374310427</v>
       </c>
       <c r="R4">
-        <v>0.8109090909090909</v>
+        <v>0.7355514125914241</v>
       </c>
       <c r="S4">
-        <v>0</v>
+        <v>40.79999999999995</v>
       </c>
       <c r="T4">
-        <v>0</v>
+        <v>0.07368611161278664</v>
       </c>
       <c r="U4">
-        <v>32.5</v>
+        <v>3203.4</v>
       </c>
       <c r="V4">
-        <v>0.1521535580524345</v>
+        <v>0.5454266839201798</v>
       </c>
       <c r="W4">
-        <v>0.4708904109589041</v>
+        <v>0.1655979861309015</v>
       </c>
       <c r="X4">
-        <v>0.08641811015164159</v>
+        <v>0.1387956874574197</v>
       </c>
       <c r="Y4">
-        <v>0.3844723008072625</v>
+        <v>0.02680229867348177</v>
       </c>
       <c r="Z4">
-        <v>5.429729729729729</v>
+        <v>47.68946301144287</v>
       </c>
       <c r="AA4">
-        <v>1.157991324657991</v>
+        <v>6.308813728406488</v>
       </c>
       <c r="AB4">
-        <v>0.08475007414259093</v>
+        <v>0.1277372774323769</v>
       </c>
       <c r="AC4">
-        <v>1.0732412505154</v>
+        <v>6.181076450974111</v>
       </c>
       <c r="AD4">
-        <v>7.71</v>
+        <v>969.6</v>
       </c>
       <c r="AE4">
-        <v>0</v>
+        <v>9.516030579074</v>
       </c>
       <c r="AF4">
-        <v>7.71</v>
+        <v>979.116030579074</v>
       </c>
       <c r="AG4">
-        <v>-24.79</v>
+        <v>-2224.283969420926</v>
       </c>
       <c r="AH4">
-        <v>0.03483801003117799</v>
+        <v>0.1428883353029372</v>
       </c>
       <c r="AI4">
-        <v>0.09243495983695001</v>
+        <v>0.1708003999214579</v>
       </c>
       <c r="AJ4">
-        <v>-0.1312960118637784</v>
+        <v>-0.6095738983250699</v>
       </c>
       <c r="AK4">
-        <v>-0.4869377332547632</v>
+        <v>-0.8794709070392661</v>
       </c>
       <c r="AL4">
-        <v>1.42</v>
+        <v>61</v>
       </c>
       <c r="AM4">
-        <v>1.42</v>
+        <v>61</v>
       </c>
       <c r="AN4">
-        <v>0.1193498452012384</v>
+        <v>0.6660164031267602</v>
       </c>
       <c r="AO4">
-        <v>44.43661971830986</v>
+        <v>23.19016393442623</v>
       </c>
       <c r="AP4">
-        <v>-0.3837461300309598</v>
+        <v>-1.527856444767159</v>
       </c>
       <c r="AQ4">
-        <v>44.43661971830986</v>
+        <v>23.19016393442623</v>
       </c>
     </row>
     <row r="5">
@@ -984,7 +975,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Discovery Limited (JSE:DSY)</t>
+          <t>Clientèle Limited (JSE:CLI)</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -993,118 +984,121 @@
         </is>
       </c>
       <c r="D5">
-        <v>0.123</v>
+        <v>0.0375</v>
       </c>
       <c r="E5">
-        <v>-0.029</v>
+        <v>-0.0137</v>
       </c>
       <c r="G5">
-        <v>0.0886156881370794</v>
+        <v>0.3308596165739023</v>
       </c>
       <c r="H5">
-        <v>0.0886156881370794</v>
+        <v>0.3308596165739023</v>
       </c>
       <c r="I5">
-        <v>0.07944539841438018</v>
+        <v>0.3228200371057514</v>
       </c>
       <c r="J5">
-        <v>0.06098292576483215</v>
+        <v>0.2125498264112125</v>
       </c>
       <c r="K5">
-        <v>225.6</v>
+        <v>26.6</v>
       </c>
       <c r="L5">
-        <v>0.04121150122392313</v>
+        <v>0.1645021645021645</v>
       </c>
       <c r="M5">
-        <v>-0</v>
+        <v>22.5</v>
       </c>
       <c r="N5">
-        <v>-0</v>
+        <v>0.1066350710900474</v>
       </c>
       <c r="O5">
-        <v>-0</v>
+        <v>0.8458646616541353</v>
       </c>
       <c r="P5">
-        <v>-0</v>
+        <v>22.5</v>
       </c>
       <c r="Q5">
-        <v>-0</v>
+        <v>0.1066350710900474</v>
       </c>
       <c r="R5">
-        <v>-0</v>
+        <v>0.8458646616541353</v>
       </c>
       <c r="S5">
         <v>0</v>
       </c>
+      <c r="T5">
+        <v>0</v>
+      </c>
       <c r="U5">
-        <v>1402.2</v>
+        <v>30.7</v>
       </c>
       <c r="V5">
-        <v>0.2361798888327438</v>
+        <v>0.1454976303317536</v>
       </c>
       <c r="W5">
-        <v>0.08942090451464584</v>
+        <v>0.3513870541611625</v>
       </c>
       <c r="X5">
-        <v>0.09647668082485035</v>
+        <v>0.1298311986067048</v>
       </c>
       <c r="Y5">
-        <v>-0.007055776310204515</v>
+        <v>0.2215558555544577</v>
       </c>
       <c r="Z5">
-        <v>2.263469092412652</v>
+        <v>3.176193282262817</v>
       </c>
       <c r="AA5">
-        <v>0.1380329676335928</v>
+        <v>0.6750993307934211</v>
       </c>
       <c r="AB5">
-        <v>0.08537337650212216</v>
+        <v>0.1279054838943774</v>
       </c>
       <c r="AC5">
-        <v>0.0526595911314706</v>
+        <v>0.5471938468990436</v>
       </c>
       <c r="AD5">
-        <v>1407.5</v>
+        <v>6.11</v>
       </c>
       <c r="AE5">
         <v>0</v>
       </c>
       <c r="AF5">
-        <v>1407.5</v>
+        <v>6.11</v>
       </c>
       <c r="AG5">
-        <v>5.299999999999955</v>
+        <v>-24.59</v>
       </c>
       <c r="AH5">
-        <v>0.1916400027231261</v>
+        <v>0.02814241628667496</v>
       </c>
       <c r="AI5">
-        <v>0.3020515901970042</v>
+        <v>0.08049005401132921</v>
       </c>
       <c r="AJ5">
-        <v>0.0008919105396900113</v>
+        <v>-0.1319135239525777</v>
       </c>
       <c r="AK5">
-        <v>0.001626964636542225</v>
+        <v>-0.5439062154390623</v>
       </c>
       <c r="AL5">
-        <v>142.5</v>
+        <v>1.39</v>
       </c>
       <c r="AM5">
-        <v>142.5</v>
+        <v>1.39</v>
       </c>
       <c r="AN5">
-        <v>2.90146361574933</v>
+        <v>0.1142056074766355</v>
       </c>
       <c r="AO5">
-        <v>3.051929824561403</v>
+        <v>37.55395683453238</v>
       </c>
       <c r="AP5">
-        <v>0.01092558235415369</v>
+        <v>-0.4596261682242991</v>
       </c>
       <c r="AQ5">
-        <v>3.051929824561403</v>
+        <v>37.55395683453238</v>
       </c>
     </row>
     <row r="6">
@@ -1115,7 +1109,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Old Mutual Limited (JSE:OMU)</t>
+          <t>Discovery Limited (JSE:DSY)</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1124,124 +1118,118 @@
         </is>
       </c>
       <c r="D6">
-        <v>-0.021</v>
+        <v>0.0864</v>
       </c>
       <c r="E6">
-        <v>-0.225</v>
-      </c>
-      <c r="F6">
-        <v>0.551</v>
+        <v>0.0404</v>
       </c>
       <c r="G6">
-        <v>-0.005977152574011213</v>
+        <v>0.1367106176266482</v>
       </c>
       <c r="H6">
-        <v>-0.005977152574011213</v>
+        <v>0.1367106176266482</v>
       </c>
       <c r="I6">
-        <v>0.04774690115004251</v>
+        <v>0.1263490392208476</v>
       </c>
       <c r="J6">
-        <v>0.02387345057502125</v>
+        <v>0.09969123863087623</v>
       </c>
       <c r="K6">
-        <v>245.8</v>
+        <v>334.6</v>
       </c>
       <c r="L6">
-        <v>0.01571319895927226</v>
+        <v>0.08006891765775684</v>
       </c>
       <c r="M6">
-        <v>126.6</v>
+        <v>-0</v>
       </c>
       <c r="N6">
-        <v>0.03275719312771683</v>
+        <v>-0</v>
       </c>
       <c r="O6">
-        <v>0.5150528885272578</v>
+        <v>-0</v>
       </c>
       <c r="P6">
-        <v>110.1</v>
+        <v>-0</v>
       </c>
       <c r="Q6">
-        <v>0.028487890705858</v>
+        <v>-0</v>
       </c>
       <c r="R6">
-        <v>0.4479251423921887</v>
+        <v>-0</v>
       </c>
       <c r="S6">
-        <v>16.5</v>
-      </c>
-      <c r="T6">
-        <v>0.1303317535545024</v>
+        <v>0</v>
       </c>
       <c r="U6">
-        <v>2274.5</v>
+        <v>1208</v>
       </c>
       <c r="V6">
-        <v>0.5885168702132063</v>
+        <v>0.250679615679927</v>
       </c>
       <c r="W6">
-        <v>0.06371341921770912</v>
+        <v>0.1046442533229085</v>
       </c>
       <c r="X6">
-        <v>0.1001215521799828</v>
+        <v>0.1450435094883651</v>
       </c>
       <c r="Y6">
-        <v>-0.03640813296227367</v>
+        <v>-0.04039925616545662</v>
       </c>
       <c r="Z6">
-        <v>5.223353813276346</v>
+        <v>1.433289888873645</v>
       </c>
       <c r="AA6">
-        <v>0.1246994790971016</v>
+        <v>0.1428864443389246</v>
       </c>
       <c r="AB6">
-        <v>0.08555202792599165</v>
+        <v>0.1276417479035706</v>
       </c>
       <c r="AC6">
-        <v>0.03914745117111</v>
+        <v>0.01524469643535395</v>
       </c>
       <c r="AD6">
-        <v>1197.7</v>
+        <v>1266</v>
       </c>
       <c r="AE6">
         <v>0</v>
       </c>
       <c r="AF6">
-        <v>1197.7</v>
+        <v>1266</v>
       </c>
       <c r="AG6">
-        <v>-1076.8</v>
+        <v>58</v>
       </c>
       <c r="AH6">
-        <v>0.2365827160493827</v>
+        <v>0.2080560074939605</v>
       </c>
       <c r="AI6">
-        <v>0.1945486737163556</v>
+        <v>0.2790082644628099</v>
       </c>
       <c r="AJ6">
-        <v>-0.3862266857962697</v>
+        <v>0.0118928007545777</v>
       </c>
       <c r="AK6">
-        <v>-0.2773970838270905</v>
+        <v>0.01742003303799369</v>
       </c>
       <c r="AL6">
-        <v>44.1</v>
+        <v>131.4</v>
       </c>
       <c r="AM6">
-        <v>44.1</v>
+        <v>131.4</v>
       </c>
       <c r="AN6">
-        <v>1.489491356796418</v>
+        <v>2.215998599684929</v>
       </c>
       <c r="AO6">
-        <v>16.93650793650794</v>
+        <v>4.018264840182648</v>
       </c>
       <c r="AP6">
-        <v>-1.33913692326825</v>
+        <v>0.1015228426395939</v>
       </c>
       <c r="AQ6">
-        <v>16.93650793650794</v>
+        <v>4.018264840182648</v>
       </c>
     </row>
     <row r="7">
@@ -1252,7 +1240,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Liberty Holdings Limited (JSE:LBH)</t>
+          <t>Old Mutual Limited (JSE:OMU)</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1261,121 +1249,124 @@
         </is>
       </c>
       <c r="D7">
-        <v>0.0499</v>
+        <v>0.211</v>
       </c>
       <c r="E7">
-        <v>-0.237</v>
+        <v>-0.06370000000000001</v>
+      </c>
+      <c r="F7">
+        <v>0.158</v>
       </c>
       <c r="G7">
-        <v>0.01029081202584996</v>
+        <v>0.0878327182069269</v>
       </c>
       <c r="H7">
-        <v>0.01029081202584996</v>
+        <v>0.0878327182069269</v>
       </c>
       <c r="I7">
-        <v>0.07489814554650183</v>
+        <v>0.06825458900593943</v>
       </c>
       <c r="J7">
-        <v>0.03744907277325091</v>
+        <v>0.05796029430954686</v>
       </c>
       <c r="K7">
-        <v>69.90000000000001</v>
+        <v>543.7</v>
       </c>
       <c r="L7">
-        <v>0.01227521775779714</v>
+        <v>0.06644587294991812</v>
       </c>
       <c r="M7">
-        <v>115.5</v>
+        <v>279.9</v>
       </c>
       <c r="N7">
-        <v>0.0740242261103634</v>
+        <v>0.09258401693569727</v>
       </c>
       <c r="O7">
-        <v>1.652360515021459</v>
+        <v>0.5148059591686591</v>
       </c>
       <c r="P7">
-        <v>107.3</v>
+        <v>208.1</v>
       </c>
       <c r="Q7">
-        <v>0.06876882650772287</v>
+        <v>0.06883434771103467</v>
       </c>
       <c r="R7">
-        <v>1.535050071530758</v>
+        <v>0.3827478388817362</v>
       </c>
       <c r="S7">
-        <v>8.200000000000003</v>
+        <v>71.79999999999998</v>
       </c>
       <c r="T7">
-        <v>0.07099567099567101</v>
+        <v>0.2565201857806359</v>
       </c>
       <c r="U7">
-        <v>1092.2</v>
+        <v>2217.7</v>
       </c>
       <c r="V7">
-        <v>0.6999935909760944</v>
+        <v>0.733560465731675</v>
       </c>
       <c r="W7">
-        <v>0.05925235229295584</v>
+        <v>0.1138710285462961</v>
       </c>
       <c r="X7">
-        <v>0.125415601430952</v>
+        <v>0.1518017468828094</v>
       </c>
       <c r="Y7">
-        <v>-0.06616324913799615</v>
+        <v>-0.03793071833651331</v>
       </c>
       <c r="Z7">
-        <v>3.352210513922411</v>
+        <v>2.212769409664945</v>
       </c>
       <c r="AA7">
-        <v>0.1255371754871372</v>
+        <v>0.1282527662233425</v>
       </c>
       <c r="AB7">
-        <v>0.08639690076026274</v>
+        <v>0.1275535263590944</v>
       </c>
       <c r="AC7">
-        <v>0.03914027472687448</v>
+        <v>0.0006992398642480524</v>
       </c>
       <c r="AD7">
-        <v>1272.1</v>
+        <v>1108.2</v>
       </c>
       <c r="AE7">
         <v>0</v>
       </c>
       <c r="AF7">
-        <v>1272.1</v>
+        <v>1108.2</v>
       </c>
       <c r="AG7">
-        <v>179.8999999999999</v>
+        <v>-1109.5</v>
       </c>
       <c r="AH7">
-        <v>0.4491244174551617</v>
+        <v>0.2682383695599555</v>
       </c>
       <c r="AI7">
-        <v>0.3911987207085306</v>
+        <v>0.2167755565118736</v>
       </c>
       <c r="AJ7">
-        <v>0.1033789219629927</v>
+        <v>-0.5797669436170767</v>
       </c>
       <c r="AK7">
-        <v>0.08330246341915164</v>
+        <v>-0.3833131801692865</v>
       </c>
       <c r="AL7">
-        <v>16</v>
+        <v>36.5</v>
       </c>
       <c r="AM7">
-        <v>16</v>
+        <v>36.5</v>
       </c>
       <c r="AN7">
-        <v>2.874152733845458</v>
+        <v>1.746847414880202</v>
       </c>
       <c r="AO7">
-        <v>26.65625</v>
+        <v>15.3013698630137</v>
       </c>
       <c r="AP7">
-        <v>0.406461816538635</v>
+        <v>-1.74889659520807</v>
       </c>
       <c r="AQ7">
-        <v>26.65625</v>
+        <v>15.3013698630137</v>
       </c>
     </row>
     <row r="8">
@@ -1386,7 +1377,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Rand Merchant Investment Holdings Limited (JSE:RMI)</t>
+          <t>OUTsurance Group Limited (JSE:OUT)</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1395,46 +1386,46 @@
         </is>
       </c>
       <c r="D8">
-        <v>0.062</v>
+        <v>0.07629999999999999</v>
       </c>
       <c r="E8">
-        <v>-0.00571</v>
+        <v>0.464</v>
       </c>
       <c r="G8">
-        <v>0.2113162239231578</v>
+        <v>0.1643762406474271</v>
       </c>
       <c r="H8">
-        <v>0.2113162239231578</v>
+        <v>0.1643762406474271</v>
       </c>
       <c r="I8">
-        <v>0.2061426274036507</v>
+        <v>0.1591768591084503</v>
       </c>
       <c r="J8">
-        <v>0.152313498912776</v>
+        <v>0.09934239228530979</v>
       </c>
       <c r="K8">
-        <v>202.7</v>
+        <v>1368.1</v>
       </c>
       <c r="L8">
-        <v>0.1521086597628696</v>
+        <v>1.044510612307223</v>
       </c>
       <c r="M8">
-        <v>24.2</v>
+        <v>55.5</v>
       </c>
       <c r="N8">
-        <v>0.005590076459310249</v>
+        <v>0.01953056269134673</v>
       </c>
       <c r="O8">
-        <v>0.1193882585101135</v>
+        <v>0.04056720999926906</v>
       </c>
       <c r="P8">
-        <v>24.2</v>
+        <v>55.5</v>
       </c>
       <c r="Q8">
-        <v>0.005590076459310249</v>
+        <v>0.01953056269134673</v>
       </c>
       <c r="R8">
-        <v>0.1193882585101135</v>
+        <v>0.04056720999926906</v>
       </c>
       <c r="S8">
         <v>0</v>
@@ -1443,207 +1434,73 @@
         <v>0</v>
       </c>
       <c r="U8">
-        <v>183.4</v>
+        <v>153.2</v>
       </c>
       <c r="V8">
-        <v>0.04236446374535122</v>
+        <v>0.05391139106872646</v>
       </c>
       <c r="W8">
-        <v>0.1360493992885428</v>
+        <v>0.7168832529867951</v>
       </c>
       <c r="X8">
-        <v>0.09403381038115209</v>
+        <v>0.1280637780697207</v>
       </c>
       <c r="Y8">
-        <v>0.04201558890739075</v>
+        <v>0.5888194749170744</v>
       </c>
       <c r="Z8">
-        <v>0.6535599360445998</v>
+        <v>0.5156488380058682</v>
       </c>
       <c r="AA8">
-        <v>0.0995460006081631</v>
+        <v>0.05122578914664312</v>
       </c>
       <c r="AB8">
-        <v>0.08471461371635422</v>
+        <v>0.1279541974205042</v>
       </c>
       <c r="AC8">
-        <v>0.01483138689180888</v>
+        <v>-0.07672840827386106</v>
       </c>
       <c r="AD8">
-        <v>815</v>
+        <v>5.01</v>
       </c>
       <c r="AE8">
-        <v>0.00667360947507816</v>
+        <v>0.100749698759241</v>
       </c>
       <c r="AF8">
-        <v>815.0066736094751</v>
+        <v>5.110749698759241</v>
       </c>
       <c r="AG8">
-        <v>631.6066736094751</v>
+        <v>-148.0892503012408</v>
       </c>
       <c r="AH8">
-        <v>0.158435025811315</v>
+        <v>0.001795254461259866</v>
       </c>
       <c r="AI8">
-        <v>0.2855257735853304</v>
+        <v>0.006418034292131073</v>
       </c>
       <c r="AJ8">
-        <v>0.1273219150347202</v>
+        <v>-0.05497796974481274</v>
       </c>
       <c r="AK8">
-        <v>0.23646765088608</v>
+        <v>-0.2302702145324231</v>
       </c>
       <c r="AL8">
-        <v>43.9</v>
+        <v>26.4</v>
       </c>
       <c r="AM8">
-        <v>43.9</v>
+        <v>26.4</v>
       </c>
       <c r="AN8">
-        <v>2.894104194853111</v>
+        <v>0.02325797316744812</v>
       </c>
       <c r="AO8">
-        <v>6.257403189066059</v>
+        <v>7.893939393939394</v>
       </c>
       <c r="AP8">
-        <v>2.242865673117057</v>
+        <v>-0.6874762095596338</v>
       </c>
       <c r="AQ8">
-        <v>6.257403189066059</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>South Africa</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>Sanlam Limited (JSE:SLM)</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Insurance (Life)</t>
-        </is>
-      </c>
-      <c r="D9">
-        <v>0.145</v>
-      </c>
-      <c r="E9">
-        <v>-0.00191</v>
-      </c>
-      <c r="G9">
-        <v>0.05586296916165507</v>
-      </c>
-      <c r="H9">
-        <v>0.05586296916165507</v>
-      </c>
-      <c r="I9">
-        <v>0.08710971596050512</v>
-      </c>
-      <c r="J9">
-        <v>0.05880376025933784</v>
-      </c>
-      <c r="K9">
-        <v>708.2</v>
-      </c>
-      <c r="L9">
-        <v>0.05671180441554489</v>
-      </c>
-      <c r="M9">
-        <v>569.5</v>
-      </c>
-      <c r="N9">
-        <v>0.07414881843629972</v>
-      </c>
-      <c r="O9">
-        <v>0.8041513696695848</v>
-      </c>
-      <c r="P9">
-        <v>517.7</v>
-      </c>
-      <c r="Q9">
-        <v>0.06740446585508757</v>
-      </c>
-      <c r="R9">
-        <v>0.7310081897768992</v>
-      </c>
-      <c r="S9">
-        <v>51.79999999999995</v>
-      </c>
-      <c r="T9">
-        <v>0.09095697980684803</v>
-      </c>
-      <c r="U9">
-        <v>4004.2</v>
-      </c>
-      <c r="V9">
-        <v>0.5213462665191068</v>
-      </c>
-      <c r="W9">
-        <v>0.193322960172522</v>
-      </c>
-      <c r="X9">
-        <v>0.09161725033228749</v>
-      </c>
-      <c r="Y9">
-        <v>0.1017057098402346</v>
-      </c>
-      <c r="Z9">
-        <v>-11.01305229738073</v>
-      </c>
-      <c r="AA9">
-        <v>-0.647608887018726</v>
-      </c>
-      <c r="AB9">
-        <v>0.08469143519252832</v>
-      </c>
-      <c r="AC9">
-        <v>-0.7323003222112543</v>
-      </c>
-      <c r="AD9">
-        <v>1075.1</v>
-      </c>
-      <c r="AE9">
-        <v>0</v>
-      </c>
-      <c r="AF9">
-        <v>1075.1</v>
-      </c>
-      <c r="AG9">
-        <v>-2929.1</v>
-      </c>
-      <c r="AH9">
-        <v>0.1227899858376353</v>
-      </c>
-      <c r="AI9">
-        <v>0.1741701362450791</v>
-      </c>
-      <c r="AJ9">
-        <v>-0.6164709348823505</v>
-      </c>
-      <c r="AK9">
-        <v>-1.350749365921143</v>
-      </c>
-      <c r="AL9">
-        <v>59.4</v>
-      </c>
-      <c r="AM9">
-        <v>59.4</v>
-      </c>
-      <c r="AN9">
-        <v>0.9504066478076378</v>
-      </c>
-      <c r="AO9">
-        <v>18.31313131313131</v>
-      </c>
-      <c r="AP9">
-        <v>-2.589374115983027</v>
-      </c>
-      <c r="AQ9">
-        <v>18.31313131313131</v>
+        <v>7.893939393939394</v>
       </c>
     </row>
   </sheetData>

--- a/research/traditional_assets/database/data/south_africa/south_africa_insurance_life.xlsx
+++ b/research/traditional_assets/database/data/south_africa/south_africa_insurance_life.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AQ8"/>
+  <dimension ref="A1:AQ7"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -579,7 +579,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -588,124 +588,124 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.08135000000000001</v>
+        <v>0.091</v>
       </c>
       <c r="E2">
-        <v>0.04485</v>
+        <v>-0.00106</v>
       </c>
       <c r="F2">
-        <v>0.158</v>
+        <v>0.0533</v>
       </c>
       <c r="G2">
-        <v>0.1639437898360222</v>
+        <v>0.09687090964010427</v>
       </c>
       <c r="H2">
-        <v>0.1639437898360222</v>
+        <v>0.09687090964010427</v>
       </c>
       <c r="I2">
-        <v>0.1294689782665797</v>
+        <v>0.266042860938361</v>
       </c>
       <c r="J2">
-        <v>0.09071045940765238</v>
+        <v>0.176173645155741</v>
       </c>
       <c r="K2">
-        <v>3197</v>
+        <v>1680.7</v>
       </c>
       <c r="L2">
-        <v>0.1209312881811132</v>
+        <v>0.06267503477388585</v>
       </c>
       <c r="M2">
-        <v>956.4999999999999</v>
+        <v>1062.6872</v>
       </c>
       <c r="N2">
-        <v>0.05265968574857684</v>
+        <v>0.05703498244973755</v>
       </c>
       <c r="O2">
-        <v>0.2991867375664685</v>
+        <v>0.6322884512405545</v>
       </c>
       <c r="P2">
-        <v>843.9</v>
+        <v>803.3872</v>
       </c>
       <c r="Q2">
-        <v>0.04646054239751594</v>
+        <v>0.04311821470357768</v>
       </c>
       <c r="R2">
-        <v>0.2639662183296841</v>
+        <v>0.4780074968763015</v>
       </c>
       <c r="S2">
-        <v>112.5999999999999</v>
+        <v>259.3</v>
       </c>
       <c r="T2">
-        <v>0.1177208572922111</v>
+        <v>0.2440040681773527</v>
       </c>
       <c r="U2">
-        <v>8567.4</v>
+        <v>7384.4</v>
       </c>
       <c r="V2">
-        <v>0.4716744293594953</v>
+        <v>0.3963246422859351</v>
       </c>
       <c r="W2">
-        <v>0.1611984950712607</v>
+        <v>0.1592908096128541</v>
       </c>
       <c r="X2">
-        <v>0.1419195984728924</v>
+        <v>0.1196727743085962</v>
       </c>
       <c r="Y2">
-        <v>0.01927889659836823</v>
+        <v>0.03961803530425789</v>
       </c>
       <c r="Z2">
-        <v>2.818802860946861</v>
+        <v>3.472553431129278</v>
       </c>
       <c r="AA2">
-        <v>0.4089928875661729</v>
+        <v>0.7837306179125202</v>
       </c>
       <c r="AB2">
-        <v>0.1276895126679738</v>
+        <v>0.1087047160730234</v>
       </c>
       <c r="AC2">
-        <v>0.2812192716671988</v>
+        <v>0.6751042793511297</v>
       </c>
       <c r="AD2">
-        <v>4148.52</v>
+        <v>3417.71</v>
       </c>
       <c r="AE2">
-        <v>9.616780277833241</v>
+        <v>9.590183954081377</v>
       </c>
       <c r="AF2">
-        <v>4158.136780277833</v>
+        <v>3427.300183954081</v>
       </c>
       <c r="AG2">
-        <v>-4409.263219722166</v>
+        <v>-3957.099816045918</v>
       </c>
       <c r="AH2">
-        <v>0.1862802865722514</v>
+        <v>0.1553661758142224</v>
       </c>
       <c r="AI2">
-        <v>0.2238646165117954</v>
+        <v>0.2027448399336473</v>
       </c>
       <c r="AJ2">
-        <v>-0.3205679180737268</v>
+        <v>-0.2696472096573934</v>
       </c>
       <c r="AK2">
-        <v>-0.4406206730927052</v>
+        <v>-0.4156573712024084</v>
       </c>
       <c r="AL2">
-        <v>398.79</v>
+        <v>760.05</v>
       </c>
       <c r="AM2">
-        <v>398.79</v>
+        <v>760.05</v>
       </c>
       <c r="AN2">
-        <v>1.145452587575551</v>
+        <v>0.4710411885909602</v>
       </c>
       <c r="AO2">
-        <v>8.582712705935453</v>
+        <v>9.385566739030327</v>
       </c>
       <c r="AP2">
-        <v>-1.217446695287105</v>
+        <v>-0.5453818494615807</v>
       </c>
       <c r="AQ2">
-        <v>8.582712705935453</v>
+        <v>9.385566739030327</v>
       </c>
     </row>
     <row r="3">
@@ -716,7 +716,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Momentum Metropolitan Holdings Limited (JSE:MTM)</t>
+          <t>Sanlam Limited (JSE:SLM)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -725,112 +725,121 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.05230000000000001</v>
+        <v>0.091</v>
       </c>
       <c r="E3">
-        <v>0.193</v>
+        <v>0.0571</v>
       </c>
       <c r="G3">
-        <v>0.1607674418604651</v>
+        <v>0.1148541689255123</v>
       </c>
       <c r="H3">
-        <v>0.1607674418604651</v>
+        <v>0.1148541689255123</v>
       </c>
       <c r="I3">
-        <v>0.1537209302325581</v>
+        <v>0.5935630449104611</v>
       </c>
       <c r="J3">
-        <v>0.07786473948626529</v>
+        <v>0.3830771839169543</v>
       </c>
       <c r="K3">
-        <v>226.7</v>
+        <v>778.4</v>
       </c>
       <c r="L3">
-        <v>0.05272093023255814</v>
+        <v>0.08439770139867722</v>
       </c>
       <c r="M3">
-        <v>44.9</v>
+        <v>598.9</v>
       </c>
       <c r="N3">
-        <v>0.03216793236853417</v>
+        <v>0.06979454369588271</v>
       </c>
       <c r="O3">
-        <v>0.1980591089545655</v>
+        <v>0.769398766700925</v>
       </c>
       <c r="P3">
-        <v>44.9</v>
+        <v>473</v>
       </c>
       <c r="Q3">
-        <v>0.03216793236853417</v>
+        <v>0.05512242305585661</v>
       </c>
       <c r="R3">
-        <v>0.1980591089545655</v>
+        <v>0.6076567317574512</v>
       </c>
       <c r="S3">
-        <v>0</v>
+        <v>125.9</v>
       </c>
       <c r="T3">
-        <v>0</v>
+        <v>0.2102187343463015</v>
       </c>
       <c r="U3">
-        <v>1754.4</v>
+        <v>1340.6</v>
       </c>
       <c r="V3">
-        <v>1.256913597936667</v>
+        <v>0.1562306984115885</v>
       </c>
       <c r="W3">
-        <v>0.1567990040116199</v>
+        <v>0.1941921963875861</v>
       </c>
       <c r="X3">
-        <v>0.164947168837823</v>
+        <v>0.1137253639785534</v>
       </c>
       <c r="Y3">
-        <v>-0.008148164826203175</v>
+        <v>0.08046683240903267</v>
+      </c>
+      <c r="Z3">
+        <v>6.035243582141169</v>
+      </c>
+      <c r="AA3">
+        <v>2.311964115699511</v>
       </c>
       <c r="AB3">
-        <v>0.1274153863894588</v>
+        <v>0.1087841894208096</v>
+      </c>
+      <c r="AC3">
+        <v>2.203179926278701</v>
       </c>
       <c r="AD3">
-        <v>793.6</v>
+        <v>806.2</v>
       </c>
       <c r="AE3">
-        <v>0</v>
+        <v>9.590183954081377</v>
       </c>
       <c r="AF3">
-        <v>793.6</v>
+        <v>815.7901839540814</v>
       </c>
       <c r="AG3">
-        <v>-960.8000000000001</v>
+        <v>-524.8098160459185</v>
       </c>
       <c r="AH3">
-        <v>0.3624737370969215</v>
+        <v>0.08681675866542202</v>
       </c>
       <c r="AI3">
-        <v>0.3420837105047631</v>
+        <v>0.1321569248185656</v>
       </c>
       <c r="AJ3">
-        <v>-2.208735632183909</v>
+        <v>-0.06514448126353173</v>
       </c>
       <c r="AK3">
-        <v>-1.699027409372238</v>
+        <v>-0.1086047807701164</v>
       </c>
       <c r="AL3">
-        <v>142.1</v>
+        <v>445.7</v>
       </c>
       <c r="AM3">
-        <v>142.1</v>
+        <v>445.7</v>
       </c>
       <c r="AN3">
-        <v>1.147982062780269</v>
+        <v>0.1466978428393366</v>
       </c>
       <c r="AO3">
-        <v>4.651653764954258</v>
+        <v>12.28113080547453</v>
       </c>
       <c r="AP3">
-        <v>-1.389845219152322</v>
+        <v>-0.09549549480878851</v>
       </c>
       <c r="AQ3">
-        <v>4.651653764954258</v>
+        <v>12.28113080547453</v>
       </c>
     </row>
     <row r="4">
@@ -841,7 +850,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Sanlam Limited (JSE:SLM)</t>
+          <t>Clientèle Limited (JSE:CLI)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -850,121 +859,121 @@
         </is>
       </c>
       <c r="D4">
-        <v>0.09210000000000002</v>
+        <v>0.0421</v>
       </c>
       <c r="E4">
-        <v>0.0493</v>
+        <v>-0.00106</v>
       </c>
       <c r="G4">
-        <v>0.2509785030408864</v>
+        <v>0.3956834532374101</v>
       </c>
       <c r="H4">
-        <v>0.2509785030408864</v>
+        <v>0.3956834532374101</v>
       </c>
       <c r="I4">
-        <v>0.1703518749785253</v>
+        <v>0.3914868105515587</v>
       </c>
       <c r="J4">
-        <v>0.1322894687845975</v>
+        <v>0.3356708692451978</v>
       </c>
       <c r="K4">
-        <v>697.3</v>
+        <v>25.9</v>
       </c>
       <c r="L4">
-        <v>0.08397663635816222</v>
+        <v>0.1552757793764988</v>
       </c>
       <c r="M4">
-        <v>553.6999999999999</v>
+        <v>21.5</v>
       </c>
       <c r="N4">
-        <v>0.09427569297827419</v>
+        <v>0.1095820591233435</v>
       </c>
       <c r="O4">
-        <v>0.7940628137100243</v>
+        <v>0.8301158301158301</v>
       </c>
       <c r="P4">
-        <v>512.9</v>
+        <v>21.5</v>
       </c>
       <c r="Q4">
-        <v>0.08732888374310427</v>
+        <v>0.1095820591233435</v>
       </c>
       <c r="R4">
-        <v>0.7355514125914241</v>
+        <v>0.8301158301158301</v>
       </c>
       <c r="S4">
-        <v>40.79999999999995</v>
+        <v>0</v>
       </c>
       <c r="T4">
-        <v>0.07368611161278664</v>
+        <v>0</v>
       </c>
       <c r="U4">
-        <v>3203.4</v>
+        <v>13.2</v>
       </c>
       <c r="V4">
-        <v>0.5454266839201798</v>
+        <v>0.06727828746177369</v>
       </c>
       <c r="W4">
-        <v>0.1655979861309015</v>
+        <v>0.3936170212765958</v>
       </c>
       <c r="X4">
-        <v>0.1387956874574197</v>
+        <v>0.1102471221494674</v>
       </c>
       <c r="Y4">
-        <v>0.02680229867348177</v>
+        <v>0.2833698991271284</v>
       </c>
       <c r="Z4">
-        <v>47.68946301144287</v>
+        <v>4.047561271536035</v>
       </c>
       <c r="AA4">
-        <v>6.308813728406488</v>
+        <v>1.3586484103397</v>
       </c>
       <c r="AB4">
-        <v>0.1277372774323769</v>
+        <v>0.1088390078686977</v>
       </c>
       <c r="AC4">
-        <v>6.181076450974111</v>
+        <v>1.249809402471002</v>
       </c>
       <c r="AD4">
-        <v>969.6</v>
+        <v>5.31</v>
       </c>
       <c r="AE4">
-        <v>9.516030579074</v>
+        <v>0</v>
       </c>
       <c r="AF4">
-        <v>979.116030579074</v>
+        <v>5.31</v>
       </c>
       <c r="AG4">
-        <v>-2224.283969420926</v>
+        <v>-7.89</v>
       </c>
       <c r="AH4">
-        <v>0.1428883353029372</v>
+        <v>0.02635104957570344</v>
       </c>
       <c r="AI4">
-        <v>0.1708003999214579</v>
+        <v>0.07853867771039787</v>
       </c>
       <c r="AJ4">
-        <v>-0.6095738983250699</v>
+        <v>-0.04189899633582921</v>
       </c>
       <c r="AK4">
-        <v>-0.8794709070392661</v>
+        <v>-0.1450101084359493</v>
       </c>
       <c r="AL4">
-        <v>61</v>
+        <v>1.35</v>
       </c>
       <c r="AM4">
-        <v>61</v>
+        <v>1.35</v>
       </c>
       <c r="AN4">
-        <v>0.6660164031267602</v>
+        <v>0.08045454545454545</v>
       </c>
       <c r="AO4">
-        <v>23.19016393442623</v>
+        <v>48.37037037037037</v>
       </c>
       <c r="AP4">
-        <v>-1.527856444767159</v>
+        <v>-0.1195454545454545</v>
       </c>
       <c r="AQ4">
-        <v>23.19016393442623</v>
+        <v>48.37037037037037</v>
       </c>
     </row>
     <row r="5">
@@ -975,7 +984,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Clientèle Limited (JSE:CLI)</t>
+          <t>Momentum Metropolitan Holdings Limited (JSE:MTM)</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -984,121 +993,121 @@
         </is>
       </c>
       <c r="D5">
-        <v>0.0375</v>
+        <v>0.109</v>
       </c>
       <c r="E5">
-        <v>-0.0137</v>
+        <v>0.259</v>
       </c>
       <c r="G5">
-        <v>0.3308596165739023</v>
+        <v>0.1052096112989617</v>
       </c>
       <c r="H5">
-        <v>0.3308596165739023</v>
+        <v>0.1052096112989617</v>
       </c>
       <c r="I5">
-        <v>0.3228200371057514</v>
+        <v>0.1013345701547024</v>
       </c>
       <c r="J5">
-        <v>0.2125498264112125</v>
+        <v>0.0506672850773512</v>
       </c>
       <c r="K5">
-        <v>26.6</v>
+        <v>230</v>
       </c>
       <c r="L5">
-        <v>0.1645021645021645</v>
+        <v>0.03441156228492773</v>
       </c>
       <c r="M5">
-        <v>22.5</v>
+        <v>161.8</v>
       </c>
       <c r="N5">
-        <v>0.1066350710900474</v>
+        <v>0.09979645963116018</v>
       </c>
       <c r="O5">
-        <v>0.8458646616541353</v>
+        <v>0.7034782608695652</v>
       </c>
       <c r="P5">
-        <v>22.5</v>
+        <v>84.59999999999999</v>
       </c>
       <c r="Q5">
-        <v>0.1066350710900474</v>
+        <v>0.05218034910257201</v>
       </c>
       <c r="R5">
-        <v>0.8458646616541353</v>
+        <v>0.3678260869565217</v>
       </c>
       <c r="S5">
-        <v>0</v>
+        <v>77.20000000000002</v>
       </c>
       <c r="T5">
-        <v>0</v>
+        <v>0.477132262051916</v>
       </c>
       <c r="U5">
-        <v>30.7</v>
+        <v>1858.9</v>
       </c>
       <c r="V5">
-        <v>0.1454976303317536</v>
+        <v>1.14654906556467</v>
       </c>
       <c r="W5">
-        <v>0.3513870541611625</v>
+        <v>0.1592908096128541</v>
       </c>
       <c r="X5">
-        <v>0.1298311986067048</v>
+        <v>0.126919964375606</v>
       </c>
       <c r="Y5">
-        <v>0.2215558555544577</v>
+        <v>0.03237084523724809</v>
       </c>
       <c r="Z5">
-        <v>3.176193282262817</v>
+        <v>15.46817866234668</v>
       </c>
       <c r="AA5">
-        <v>0.6750993307934211</v>
+        <v>0.7837306179125202</v>
       </c>
       <c r="AB5">
-        <v>0.1279054838943774</v>
+        <v>0.1086263385613905</v>
       </c>
       <c r="AC5">
-        <v>0.5471938468990436</v>
+        <v>0.6751042793511297</v>
       </c>
       <c r="AD5">
-        <v>6.11</v>
+        <v>572.4</v>
       </c>
       <c r="AE5">
         <v>0</v>
       </c>
       <c r="AF5">
-        <v>6.11</v>
+        <v>572.4</v>
       </c>
       <c r="AG5">
-        <v>-24.59</v>
+        <v>-1286.5</v>
       </c>
       <c r="AH5">
-        <v>0.02814241628667496</v>
+        <v>0.2609290240233396</v>
       </c>
       <c r="AI5">
-        <v>0.08049005401132921</v>
+        <v>0.2842246387606137</v>
       </c>
       <c r="AJ5">
-        <v>-0.1319135239525777</v>
+        <v>-3.842592592592593</v>
       </c>
       <c r="AK5">
-        <v>-0.5439062154390623</v>
+        <v>-8.300000000000001</v>
       </c>
       <c r="AL5">
-        <v>1.39</v>
+        <v>135.7</v>
       </c>
       <c r="AM5">
-        <v>1.39</v>
+        <v>135.7</v>
       </c>
       <c r="AN5">
-        <v>0.1142056074766355</v>
+        <v>0.8139931740614333</v>
       </c>
       <c r="AO5">
-        <v>37.55395683453238</v>
+        <v>4.991156963890936</v>
       </c>
       <c r="AP5">
-        <v>-0.4596261682242991</v>
+        <v>-1.829493742889647</v>
       </c>
       <c r="AQ5">
-        <v>37.55395683453238</v>
+        <v>4.991156963890936</v>
       </c>
     </row>
     <row r="6">
@@ -1118,118 +1127,121 @@
         </is>
       </c>
       <c r="D6">
-        <v>0.0864</v>
+        <v>0.106</v>
       </c>
       <c r="E6">
-        <v>0.0404</v>
+        <v>-0.0147</v>
       </c>
       <c r="G6">
-        <v>0.1367106176266482</v>
+        <v>0.119845832525892</v>
       </c>
       <c r="H6">
-        <v>0.1367106176266482</v>
+        <v>0.119845832525892</v>
       </c>
       <c r="I6">
-        <v>0.1263490392208476</v>
+        <v>0.1116852916478264</v>
       </c>
       <c r="J6">
-        <v>0.09969123863087623</v>
+        <v>0.08061087095173977</v>
       </c>
       <c r="K6">
-        <v>334.6</v>
+        <v>282.8</v>
       </c>
       <c r="L6">
-        <v>0.08006891765775684</v>
+        <v>0.06089184591865297</v>
       </c>
       <c r="M6">
-        <v>-0</v>
+        <v>38.1872</v>
       </c>
       <c r="N6">
-        <v>-0</v>
+        <v>0.00738359210348228</v>
       </c>
       <c r="O6">
-        <v>-0</v>
+        <v>0.135032531824611</v>
       </c>
       <c r="P6">
-        <v>-0</v>
+        <v>38.1872</v>
       </c>
       <c r="Q6">
-        <v>-0</v>
+        <v>0.00738359210348228</v>
       </c>
       <c r="R6">
-        <v>-0</v>
+        <v>0.135032531824611</v>
       </c>
       <c r="S6">
         <v>0</v>
       </c>
+      <c r="T6">
+        <v>0</v>
+      </c>
       <c r="U6">
-        <v>1208</v>
+        <v>1081.5</v>
       </c>
       <c r="V6">
-        <v>0.250679615679927</v>
+        <v>0.2091107716699859</v>
       </c>
       <c r="W6">
-        <v>0.1046442533229085</v>
+        <v>0.08772800595607395</v>
       </c>
       <c r="X6">
-        <v>0.1450435094883651</v>
+        <v>0.1196727743085962</v>
       </c>
       <c r="Y6">
-        <v>-0.04039925616545662</v>
+        <v>-0.03194476835252223</v>
       </c>
       <c r="Z6">
-        <v>1.433289888873645</v>
+        <v>1.533227691393483</v>
       </c>
       <c r="AA6">
-        <v>0.1428864443389246</v>
+        <v>0.123594819570554</v>
       </c>
       <c r="AB6">
-        <v>0.1276417479035706</v>
+        <v>0.1087047160730234</v>
       </c>
       <c r="AC6">
-        <v>0.01524469643535395</v>
+        <v>0.01489010349753059</v>
       </c>
       <c r="AD6">
-        <v>1266</v>
+        <v>1093.1</v>
       </c>
       <c r="AE6">
         <v>0</v>
       </c>
       <c r="AF6">
-        <v>1266</v>
+        <v>1093.1</v>
       </c>
       <c r="AG6">
-        <v>58</v>
+        <v>11.59999999999991</v>
       </c>
       <c r="AH6">
-        <v>0.2080560074939605</v>
+        <v>0.1744772545889864</v>
       </c>
       <c r="AI6">
-        <v>0.2790082644628099</v>
+        <v>0.243473806129722</v>
       </c>
       <c r="AJ6">
-        <v>0.0118928007545777</v>
+        <v>0.002237870164946447</v>
       </c>
       <c r="AK6">
-        <v>0.01742003303799369</v>
+        <v>0.00340365599600948</v>
       </c>
       <c r="AL6">
-        <v>131.4</v>
+        <v>142.5</v>
       </c>
       <c r="AM6">
-        <v>131.4</v>
+        <v>142.5</v>
       </c>
       <c r="AN6">
-        <v>2.215998599684929</v>
+        <v>1.963887890765361</v>
       </c>
       <c r="AO6">
-        <v>4.018264840182648</v>
+        <v>3.64</v>
       </c>
       <c r="AP6">
-        <v>0.1015228426395939</v>
+        <v>0.02084081925979143</v>
       </c>
       <c r="AQ6">
-        <v>4.018264840182648</v>
+        <v>3.64</v>
       </c>
     </row>
     <row r="7">
@@ -1249,258 +1261,124 @@
         </is>
       </c>
       <c r="D7">
-        <v>0.211</v>
+        <v>-0.073</v>
       </c>
       <c r="E7">
-        <v>-0.06370000000000001</v>
+        <v>-0.191</v>
       </c>
       <c r="F7">
-        <v>0.158</v>
+        <v>0.0533</v>
       </c>
       <c r="G7">
-        <v>0.0878327182069269</v>
+        <v>0.03486274638417894</v>
       </c>
       <c r="H7">
-        <v>0.0878327182069269</v>
+        <v>0.03486274638417894</v>
       </c>
       <c r="I7">
-        <v>0.06825458900593943</v>
+        <v>0.06534715161851039</v>
       </c>
       <c r="J7">
-        <v>0.05796029430954686</v>
+        <v>0.038320980107149</v>
       </c>
       <c r="K7">
-        <v>543.7</v>
+        <v>363.6</v>
       </c>
       <c r="L7">
-        <v>0.06644587294991812</v>
+        <v>0.05962415138893445</v>
       </c>
       <c r="M7">
-        <v>279.9</v>
+        <v>242.3</v>
       </c>
       <c r="N7">
-        <v>0.09258401693569727</v>
+        <v>0.07913387112577158</v>
       </c>
       <c r="O7">
-        <v>0.5148059591686591</v>
+        <v>0.6663916391639164</v>
       </c>
       <c r="P7">
-        <v>208.1</v>
+        <v>186.1</v>
       </c>
       <c r="Q7">
-        <v>0.06883434771103467</v>
+        <v>0.06077925471112707</v>
       </c>
       <c r="R7">
-        <v>0.3827478388817362</v>
+        <v>0.5118261826182617</v>
       </c>
       <c r="S7">
-        <v>71.79999999999998</v>
+        <v>56.20000000000002</v>
       </c>
       <c r="T7">
-        <v>0.2565201857806359</v>
+        <v>0.2319438712340075</v>
       </c>
       <c r="U7">
-        <v>2217.7</v>
+        <v>3090.2</v>
       </c>
       <c r="V7">
-        <v>0.733560465731675</v>
+        <v>1.009242627126947</v>
       </c>
       <c r="W7">
-        <v>0.1138710285462961</v>
+        <v>0.09565400399873725</v>
       </c>
       <c r="X7">
-        <v>0.1518017468828094</v>
+        <v>0.1245763315291323</v>
       </c>
       <c r="Y7">
-        <v>-0.03793071833651331</v>
+        <v>-0.0289223275303951</v>
       </c>
       <c r="Z7">
-        <v>2.212769409664945</v>
+        <v>2.265557082884423</v>
       </c>
       <c r="AA7">
-        <v>0.1282527662233425</v>
+        <v>0.08681836790482446</v>
       </c>
       <c r="AB7">
-        <v>0.1275535263590944</v>
+        <v>0.1086498257569502</v>
       </c>
       <c r="AC7">
-        <v>0.0006992398642480524</v>
+        <v>-0.02183145785212572</v>
       </c>
       <c r="AD7">
-        <v>1108.2</v>
+        <v>940.7</v>
       </c>
       <c r="AE7">
         <v>0</v>
       </c>
       <c r="AF7">
-        <v>1108.2</v>
+        <v>940.7</v>
       </c>
       <c r="AG7">
-        <v>-1109.5</v>
+        <v>-2149.5</v>
       </c>
       <c r="AH7">
-        <v>0.2682383695599555</v>
+        <v>0.2350222355468945</v>
       </c>
       <c r="AI7">
-        <v>0.2167755565118736</v>
+        <v>0.2261026318952049</v>
       </c>
       <c r="AJ7">
-        <v>-0.5797669436170767</v>
+        <v>-2.355874616396317</v>
       </c>
       <c r="AK7">
-        <v>-0.3833131801692865</v>
+        <v>-2.008315425581612</v>
       </c>
       <c r="AL7">
-        <v>36.5</v>
+        <v>34.8</v>
       </c>
       <c r="AM7">
-        <v>36.5</v>
+        <v>34.8</v>
       </c>
       <c r="AN7">
-        <v>1.746847414880202</v>
+        <v>2.166513127590972</v>
       </c>
       <c r="AO7">
-        <v>15.3013698630137</v>
+        <v>11.45114942528736</v>
       </c>
       <c r="AP7">
-        <v>-1.74889659520807</v>
+        <v>-4.950483648088438</v>
       </c>
       <c r="AQ7">
-        <v>15.3013698630137</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>South Africa</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>OUTsurance Group Limited (JSE:OUT)</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Insurance (Life)</t>
-        </is>
-      </c>
-      <c r="D8">
-        <v>0.07629999999999999</v>
-      </c>
-      <c r="E8">
-        <v>0.464</v>
-      </c>
-      <c r="G8">
-        <v>0.1643762406474271</v>
-      </c>
-      <c r="H8">
-        <v>0.1643762406474271</v>
-      </c>
-      <c r="I8">
-        <v>0.1591768591084503</v>
-      </c>
-      <c r="J8">
-        <v>0.09934239228530979</v>
-      </c>
-      <c r="K8">
-        <v>1368.1</v>
-      </c>
-      <c r="L8">
-        <v>1.044510612307223</v>
-      </c>
-      <c r="M8">
-        <v>55.5</v>
-      </c>
-      <c r="N8">
-        <v>0.01953056269134673</v>
-      </c>
-      <c r="O8">
-        <v>0.04056720999926906</v>
-      </c>
-      <c r="P8">
-        <v>55.5</v>
-      </c>
-      <c r="Q8">
-        <v>0.01953056269134673</v>
-      </c>
-      <c r="R8">
-        <v>0.04056720999926906</v>
-      </c>
-      <c r="S8">
-        <v>0</v>
-      </c>
-      <c r="T8">
-        <v>0</v>
-      </c>
-      <c r="U8">
-        <v>153.2</v>
-      </c>
-      <c r="V8">
-        <v>0.05391139106872646</v>
-      </c>
-      <c r="W8">
-        <v>0.7168832529867951</v>
-      </c>
-      <c r="X8">
-        <v>0.1280637780697207</v>
-      </c>
-      <c r="Y8">
-        <v>0.5888194749170744</v>
-      </c>
-      <c r="Z8">
-        <v>0.5156488380058682</v>
-      </c>
-      <c r="AA8">
-        <v>0.05122578914664312</v>
-      </c>
-      <c r="AB8">
-        <v>0.1279541974205042</v>
-      </c>
-      <c r="AC8">
-        <v>-0.07672840827386106</v>
-      </c>
-      <c r="AD8">
-        <v>5.01</v>
-      </c>
-      <c r="AE8">
-        <v>0.100749698759241</v>
-      </c>
-      <c r="AF8">
-        <v>5.110749698759241</v>
-      </c>
-      <c r="AG8">
-        <v>-148.0892503012408</v>
-      </c>
-      <c r="AH8">
-        <v>0.001795254461259866</v>
-      </c>
-      <c r="AI8">
-        <v>0.006418034292131073</v>
-      </c>
-      <c r="AJ8">
-        <v>-0.05497796974481274</v>
-      </c>
-      <c r="AK8">
-        <v>-0.2302702145324231</v>
-      </c>
-      <c r="AL8">
-        <v>26.4</v>
-      </c>
-      <c r="AM8">
-        <v>26.4</v>
-      </c>
-      <c r="AN8">
-        <v>0.02325797316744812</v>
-      </c>
-      <c r="AO8">
-        <v>7.893939393939394</v>
-      </c>
-      <c r="AP8">
-        <v>-0.6874762095596338</v>
-      </c>
-      <c r="AQ8">
-        <v>7.893939393939394</v>
+        <v>11.45114942528736</v>
       </c>
     </row>
   </sheetData>
